--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125121813</v>
+        <v>125126976</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596348</v>
+        <v>596409</v>
       </c>
       <c r="R2" t="n">
-        <v>6924619</v>
+        <v>6924486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125126936</v>
+        <v>125120869</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -823,7 +833,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596309</v>
+        <v>596348</v>
       </c>
       <c r="R3" t="n">
-        <v>6924544</v>
+        <v>6924552</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +907,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125126976</v>
+        <v>125121984</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -945,7 +955,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596409</v>
+        <v>596332</v>
       </c>
       <c r="R4" t="n">
-        <v>6924486</v>
+        <v>6924612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125126464</v>
+        <v>125126936</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,16 +1052,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1076,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596305</v>
+        <v>596309</v>
       </c>
       <c r="R5" t="n">
-        <v>6924608</v>
+        <v>6924544</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1126,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123531</v>
+        <v>125123659</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,39 +1174,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596208</v>
+        <v>596186</v>
       </c>
       <c r="R6" t="n">
-        <v>6924703</v>
+        <v>6924711</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125123156</v>
+        <v>125126464</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,16 +1286,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1301,7 +1306,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1310,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596286</v>
+        <v>596305</v>
       </c>
       <c r="R7" t="n">
-        <v>6924710</v>
+        <v>6924608</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,22 +1375,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125120869</v>
+        <v>125123246</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,43 +1399,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596348</v>
+        <v>596268</v>
       </c>
       <c r="R8" t="n">
-        <v>6924552</v>
+        <v>6924738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,12 +1472,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Rikligt med revlummer</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125126858</v>
+        <v>125122523</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,53 +1520,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596293</v>
+        <v>596319</v>
       </c>
       <c r="R9" t="n">
-        <v>6924558</v>
+        <v>6924626</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1613,7 +1594,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,22 +1614,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125121863</v>
+        <v>125126271</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1656,27 +1642,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1685,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596311</v>
+        <v>596310</v>
       </c>
       <c r="R10" t="n">
-        <v>6924570</v>
+        <v>6924614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1730,7 +1716,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125126271</v>
+        <v>125123531</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1773,16 +1764,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1802,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596310</v>
+        <v>596208</v>
       </c>
       <c r="R11" t="n">
-        <v>6924614</v>
+        <v>6924703</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1847,12 +1838,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1879,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125123659</v>
+        <v>125126858</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1895,34 +1881,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596186</v>
+        <v>596293</v>
       </c>
       <c r="R12" t="n">
-        <v>6924711</v>
+        <v>6924558</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1959,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,7 +1969,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,22 +1984,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125123246</v>
+        <v>125121336</v>
       </c>
       <c r="B13" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,34 +2012,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596268</v>
+        <v>596327</v>
       </c>
       <c r="R13" t="n">
-        <v>6924738</v>
+        <v>6924526</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2066,7 +2076,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2076,12 +2086,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,10 +2113,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125121984</v>
+        <v>125122129</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,43 +2125,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596332</v>
+        <v>596387</v>
       </c>
       <c r="R14" t="n">
-        <v>6924612</v>
+        <v>6924499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,7 +2193,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2198,7 +2203,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Två talltitor I gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,22 +2223,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125122129</v>
+        <v>125121813</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>96979</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2237,43 +2247,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596387</v>
+        <v>596348</v>
       </c>
       <c r="R15" t="n">
-        <v>6924499</v>
+        <v>6924619</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2305,7 +2310,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2315,12 +2320,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Två talltitor I gran</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2335,19 +2335,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125125242</v>
+        <v>125123156</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2383,7 +2383,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596305</v>
+        <v>596286</v>
       </c>
       <c r="R16" t="n">
-        <v>6924653</v>
+        <v>6924710</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125121336</v>
+        <v>125121863</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,31 +2481,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596327</v>
+        <v>596311</v>
       </c>
       <c r="R17" t="n">
-        <v>6924526</v>
+        <v>6924570</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,7 +2586,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125122523</v>
+        <v>125125242</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596319</v>
+        <v>596305</v>
       </c>
       <c r="R18" t="n">
-        <v>6924626</v>
+        <v>6924653</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125120869</v>
+        <v>125125242</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -833,7 +833,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596348</v>
+        <v>596305</v>
       </c>
       <c r="R3" t="n">
-        <v>6924552</v>
+        <v>6924653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125121984</v>
+        <v>125123659</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,43 +931,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596332</v>
+        <v>596186</v>
       </c>
       <c r="R4" t="n">
-        <v>6924612</v>
+        <v>6924711</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125126936</v>
+        <v>125123156</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1072,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1081,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596309</v>
+        <v>596286</v>
       </c>
       <c r="R5" t="n">
-        <v>6924544</v>
+        <v>6924710</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,22 +1141,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123659</v>
+        <v>125121863</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,34 +1169,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596186</v>
+        <v>596311</v>
       </c>
       <c r="R6" t="n">
-        <v>6924711</v>
+        <v>6924570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125126464</v>
+        <v>125126330</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1306,7 +1306,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596305</v>
+        <v>596310</v>
       </c>
       <c r="R7" t="n">
-        <v>6924608</v>
+        <v>6924614</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1360,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,22 +1380,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123246</v>
+        <v>125121984</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>57883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,34 +1408,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596268</v>
+        <v>596332</v>
       </c>
       <c r="R8" t="n">
-        <v>6924738</v>
+        <v>6924612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,12 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125122523</v>
+        <v>125123246</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,43 +1521,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596319</v>
+        <v>596268</v>
       </c>
       <c r="R9" t="n">
-        <v>6924626</v>
+        <v>6924738</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
+          <t>Rikligt med revlummer</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,7 +1626,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125126271</v>
+        <v>125120869</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596310</v>
+        <v>596348</v>
       </c>
       <c r="R10" t="n">
-        <v>6924614</v>
+        <v>6924552</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125123531</v>
+        <v>125126858</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,39 +1764,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596208</v>
+        <v>596293</v>
       </c>
       <c r="R11" t="n">
-        <v>6924703</v>
+        <v>6924558</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,7 +1842,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,7 +1852,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,22 +1867,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125126858</v>
+        <v>125121813</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>96979</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,57 +1891,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596293</v>
+        <v>596348</v>
       </c>
       <c r="R12" t="n">
-        <v>6924558</v>
+        <v>6924619</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1959,7 +1954,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1969,7 +1964,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,22 +1979,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125121336</v>
+        <v>125126464</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2008,31 +2003,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2041,10 +2036,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596327</v>
+        <v>596305</v>
       </c>
       <c r="R13" t="n">
-        <v>6924526</v>
+        <v>6924608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,7 +2071,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2086,7 +2081,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2101,22 +2096,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125122129</v>
+        <v>125121336</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2125,43 +2120,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596387</v>
+        <v>596327</v>
       </c>
       <c r="R14" t="n">
-        <v>6924499</v>
+        <v>6924526</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2193,7 +2188,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2203,12 +2198,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Två talltitor I gran</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2223,22 +2213,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125121813</v>
+        <v>125122523</v>
       </c>
       <c r="B15" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,38 +2237,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596348</v>
+        <v>596319</v>
       </c>
       <c r="R15" t="n">
-        <v>6924619</v>
+        <v>6924626</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2310,7 +2305,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2320,7 +2315,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2347,10 +2347,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125123156</v>
+        <v>125123531</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2363,16 +2363,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596286</v>
+        <v>596208</v>
       </c>
       <c r="R16" t="n">
-        <v>6924710</v>
+        <v>6924703</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,12 +2437,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,10 +2464,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125121863</v>
+        <v>125126936</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2485,27 +2480,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2514,10 +2509,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596311</v>
+        <v>596309</v>
       </c>
       <c r="R17" t="n">
-        <v>6924570</v>
+        <v>6924544</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2549,7 +2544,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2559,7 +2554,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,22 +2574,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125125242</v>
+        <v>125122129</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2602,39 +2602,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596305</v>
+        <v>596387</v>
       </c>
       <c r="R18" t="n">
-        <v>6924653</v>
+        <v>6924499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Två talltitor I gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,12 +2696,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -1626,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125120869</v>
+        <v>125126858</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,39 +1642,53 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596348</v>
+        <v>596293</v>
       </c>
       <c r="R10" t="n">
-        <v>6924552</v>
+        <v>6924558</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1720,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,12 +1730,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,22 +1745,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125126858</v>
+        <v>125120869</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,53 +1773,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596293</v>
+        <v>596348</v>
       </c>
       <c r="R11" t="n">
-        <v>6924558</v>
+        <v>6924552</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,7 +1837,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1852,7 +1847,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,12 +1867,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -1626,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125126858</v>
+        <v>125120869</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,53 +1642,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596293</v>
+        <v>596348</v>
       </c>
       <c r="R10" t="n">
-        <v>6924558</v>
+        <v>6924552</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1730,7 +1716,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,22 +1736,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125120869</v>
+        <v>125126858</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1773,39 +1764,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596348</v>
+        <v>596293</v>
       </c>
       <c r="R11" t="n">
-        <v>6924552</v>
+        <v>6924558</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,7 +1842,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1847,12 +1852,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,12 +1867,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125126976</v>
+        <v>125126858</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,53 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596409</v>
+        <v>596293</v>
       </c>
       <c r="R2" t="n">
-        <v>6924486</v>
+        <v>6924558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,19 +794,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125125242</v>
+        <v>125126936</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -842,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596305</v>
+        <v>596309</v>
       </c>
       <c r="R3" t="n">
-        <v>6924653</v>
+        <v>6924544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +896,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,22 +916,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123659</v>
+        <v>125123156</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +944,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596186</v>
+        <v>596286</v>
       </c>
       <c r="R4" t="n">
-        <v>6924711</v>
+        <v>6924710</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1018,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125123156</v>
+        <v>125120869</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1076,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596286</v>
+        <v>596348</v>
       </c>
       <c r="R5" t="n">
-        <v>6924710</v>
+        <v>6924552</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1140,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,7 +1172,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125121863</v>
+        <v>125122129</v>
       </c>
       <c r="B6" t="n">
         <v>57666</v>
@@ -1194,14 +1213,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596311</v>
+        <v>596387</v>
       </c>
       <c r="R6" t="n">
-        <v>6924570</v>
+        <v>6924499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1252,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1262,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Två talltitor I gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,22 +1282,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125126330</v>
+        <v>125121813</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,43 +1306,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596310</v>
+        <v>596348</v>
       </c>
       <c r="R7" t="n">
-        <v>6924614</v>
+        <v>6924619</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,12 +1379,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,10 +1406,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125121984</v>
+        <v>125126464</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,20 +1418,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1428,7 +1442,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1437,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596332</v>
+        <v>596305</v>
       </c>
       <c r="R8" t="n">
-        <v>6924612</v>
+        <v>6924608</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,22 +1511,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125123246</v>
+        <v>125126976</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,38 +1535,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596268</v>
+        <v>596409</v>
       </c>
       <c r="R9" t="n">
-        <v>6924738</v>
+        <v>6924486</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1603,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1613,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt med revlummer</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,7 +1645,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125120869</v>
+        <v>125126271</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1671,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596348</v>
+        <v>596310</v>
       </c>
       <c r="R10" t="n">
-        <v>6924552</v>
+        <v>6924614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1725,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1735,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1748,10 +1767,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125126858</v>
+        <v>125122523</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,53 +1783,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596293</v>
+        <v>596319</v>
       </c>
       <c r="R11" t="n">
-        <v>6924558</v>
+        <v>6924626</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,7 +1847,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1852,7 +1857,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,22 +1877,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125121813</v>
+        <v>125123659</v>
       </c>
       <c r="B12" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,25 +1901,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1919,10 +1929,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596348</v>
+        <v>596186</v>
       </c>
       <c r="R12" t="n">
-        <v>6924619</v>
+        <v>6924711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1964,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,7 +1974,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,7 +2001,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125126464</v>
+        <v>125123531</v>
       </c>
       <c r="B13" t="n">
         <v>57529</v>
@@ -2027,7 +2037,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2036,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596305</v>
+        <v>596208</v>
       </c>
       <c r="R13" t="n">
-        <v>6924608</v>
+        <v>6924703</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2071,7 +2081,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2081,7 +2091,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,22 +2106,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125121336</v>
+        <v>125125242</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,31 +2130,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2153,10 +2163,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596327</v>
+        <v>596305</v>
       </c>
       <c r="R14" t="n">
-        <v>6924526</v>
+        <v>6924653</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,7 +2198,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2198,7 +2208,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,10 +2240,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125122523</v>
+        <v>125121984</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2237,20 +2252,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2261,7 +2276,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2270,10 +2285,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596319</v>
+        <v>596332</v>
       </c>
       <c r="R15" t="n">
-        <v>6924626</v>
+        <v>6924612</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2305,7 +2320,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2315,12 +2330,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2347,10 +2357,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125123531</v>
+        <v>125121863</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2363,27 +2373,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2392,10 +2402,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596208</v>
+        <v>596311</v>
       </c>
       <c r="R16" t="n">
-        <v>6924703</v>
+        <v>6924570</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,7 +2437,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,7 +2447,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2464,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125126936</v>
+        <v>125123246</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2476,43 +2486,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596309</v>
+        <v>596268</v>
       </c>
       <c r="R17" t="n">
-        <v>6924544</v>
+        <v>6924738</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2544,7 +2549,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2554,12 +2559,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Rikligt med revlummer</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,22 +2579,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125122129</v>
+        <v>125121336</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2598,43 +2603,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596387</v>
+        <v>596327</v>
       </c>
       <c r="R18" t="n">
-        <v>6924499</v>
+        <v>6924526</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2666,7 +2671,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2676,12 +2681,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två talltitor I gran</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,12 +2696,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125126858</v>
+        <v>125123531</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,53 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596293</v>
+        <v>596208</v>
       </c>
       <c r="R2" t="n">
-        <v>6924558</v>
+        <v>6924703</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,19 +780,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125126936</v>
+        <v>125123156</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -842,7 +828,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596309</v>
+        <v>596286</v>
       </c>
       <c r="R3" t="n">
-        <v>6924544</v>
+        <v>6924710</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,19 +902,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123156</v>
+        <v>125126330</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -973,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596286</v>
+        <v>596310</v>
       </c>
       <c r="R4" t="n">
-        <v>6924710</v>
+        <v>6924614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,12 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1036,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125120869</v>
+        <v>125125242</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1086,7 +1072,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1095,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596348</v>
+        <v>596305</v>
       </c>
       <c r="R5" t="n">
-        <v>6924552</v>
+        <v>6924653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1172,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125122129</v>
+        <v>125122523</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,39 +1174,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596387</v>
+        <v>596319</v>
       </c>
       <c r="R6" t="n">
-        <v>6924499</v>
+        <v>6924626</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1262,12 +1248,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Två talltitor I gran</t>
+          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,22 +1268,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125121813</v>
+        <v>125126858</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,38 +1292,57 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596348</v>
+        <v>596293</v>
       </c>
       <c r="R7" t="n">
-        <v>6924619</v>
+        <v>6924558</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,7 +1374,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,7 +1384,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,22 +1399,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125126464</v>
+        <v>125123246</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,43 +1423,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596305</v>
+        <v>596268</v>
       </c>
       <c r="R8" t="n">
-        <v>6924608</v>
+        <v>6924738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1496,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,12 +1516,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1645,10 +1650,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125126271</v>
+        <v>125126464</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,16 +1666,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1681,7 +1686,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596310</v>
+        <v>596305</v>
       </c>
       <c r="R10" t="n">
-        <v>6924614</v>
+        <v>6924608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1725,7 +1730,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,12 +1740,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,22 +1755,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125122523</v>
+        <v>125121863</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1783,27 +1783,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596319</v>
+        <v>596311</v>
       </c>
       <c r="R11" t="n">
-        <v>6924626</v>
+        <v>6924570</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1857,12 +1857,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,10 +1884,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125123659</v>
+        <v>125121984</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1901,38 +1896,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596186</v>
+        <v>596332</v>
       </c>
       <c r="R12" t="n">
-        <v>6924711</v>
+        <v>6924612</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125123531</v>
+        <v>125123659</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,39 +2017,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596208</v>
+        <v>596186</v>
       </c>
       <c r="R13" t="n">
-        <v>6924703</v>
+        <v>6924711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2081,7 +2076,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2091,7 +2086,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,7 +2113,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125125242</v>
+        <v>125126936</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596305</v>
+        <v>596309</v>
       </c>
       <c r="R14" t="n">
-        <v>6924653</v>
+        <v>6924544</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2198,7 +2193,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2208,12 +2203,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,22 +2223,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125121984</v>
+        <v>125122129</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,43 +2247,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596332</v>
+        <v>596387</v>
       </c>
       <c r="R15" t="n">
-        <v>6924612</v>
+        <v>6924499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2320,7 +2315,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2330,7 +2325,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Två talltitor I gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2345,22 +2345,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125121863</v>
+        <v>125121813</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>96979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2369,43 +2369,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596311</v>
+        <v>596348</v>
       </c>
       <c r="R16" t="n">
-        <v>6924570</v>
+        <v>6924619</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2437,7 +2432,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2447,7 +2442,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2474,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125123246</v>
+        <v>125121336</v>
       </c>
       <c r="B17" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2490,34 +2485,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596268</v>
+        <v>596327</v>
       </c>
       <c r="R17" t="n">
-        <v>6924738</v>
+        <v>6924526</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2559,12 +2559,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2591,10 +2586,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125121336</v>
+        <v>125120869</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2603,31 +2598,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2636,10 +2631,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596327</v>
+        <v>596348</v>
       </c>
       <c r="R18" t="n">
-        <v>6924526</v>
+        <v>6924552</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2671,7 +2666,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2681,7 +2676,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123531</v>
+        <v>125126464</v>
       </c>
       <c r="B2" t="n">
         <v>57529</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596208</v>
+        <v>596305</v>
       </c>
       <c r="R2" t="n">
-        <v>6924703</v>
+        <v>6924608</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123156</v>
+        <v>125123531</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596286</v>
+        <v>596208</v>
       </c>
       <c r="R3" t="n">
-        <v>6924710</v>
+        <v>6924703</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125126330</v>
+        <v>125122129</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,39 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596310</v>
+        <v>596387</v>
       </c>
       <c r="R4" t="n">
-        <v>6924614</v>
+        <v>6924499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Två talltitor I gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125125242</v>
+        <v>125121863</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,27 +1047,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1081,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596305</v>
+        <v>596311</v>
       </c>
       <c r="R5" t="n">
-        <v>6924653</v>
+        <v>6924570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,12 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,7 +1148,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125122523</v>
+        <v>125125242</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1203,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596319</v>
+        <v>596305</v>
       </c>
       <c r="R6" t="n">
-        <v>6924626</v>
+        <v>6924653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,12 +1238,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125126858</v>
+        <v>125121984</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,57 +1282,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596293</v>
+        <v>596332</v>
       </c>
       <c r="R7" t="n">
-        <v>6924558</v>
+        <v>6924612</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1374,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1384,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,12 +1375,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1528,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125126976</v>
+        <v>125121336</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,31 +1516,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1573,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596409</v>
+        <v>596327</v>
       </c>
       <c r="R9" t="n">
-        <v>6924486</v>
+        <v>6924526</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1618,12 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125126464</v>
+        <v>125123156</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1666,16 +1637,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1686,7 +1657,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1695,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596305</v>
+        <v>596286</v>
       </c>
       <c r="R10" t="n">
-        <v>6924608</v>
+        <v>6924710</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1740,7 +1711,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,19 +1731,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125121863</v>
+        <v>125126858</v>
       </c>
       <c r="B11" t="n">
         <v>57666</v>
@@ -1800,22 +1776,36 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596311</v>
+        <v>596293</v>
       </c>
       <c r="R11" t="n">
-        <v>6924570</v>
+        <v>6924558</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1847,7 +1837,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1857,7 +1847,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1872,22 +1862,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125121984</v>
+        <v>125122523</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,20 +1886,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1920,7 +1910,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1929,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596332</v>
+        <v>596319</v>
       </c>
       <c r="R12" t="n">
-        <v>6924612</v>
+        <v>6924626</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,7 +1954,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1964,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,10 +1996,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125123659</v>
+        <v>125126976</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,34 +2012,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596186</v>
+        <v>596409</v>
       </c>
       <c r="R13" t="n">
-        <v>6924711</v>
+        <v>6924486</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2086,7 +2086,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2235,10 +2240,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125122129</v>
+        <v>125126271</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,39 +2256,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596387</v>
+        <v>596310</v>
       </c>
       <c r="R15" t="n">
-        <v>6924499</v>
+        <v>6924614</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2315,7 +2320,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2325,12 +2330,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Två talltitor I gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2345,22 +2350,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125121813</v>
+        <v>125120869</v>
       </c>
       <c r="B16" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2369,28 +2374,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
@@ -2400,7 +2410,7 @@
         <v>596348</v>
       </c>
       <c r="R16" t="n">
-        <v>6924619</v>
+        <v>6924552</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2432,7 +2442,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2442,7 +2452,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,10 +2484,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125121336</v>
+        <v>125123659</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,43 +2496,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596327</v>
+        <v>596186</v>
       </c>
       <c r="R17" t="n">
-        <v>6924526</v>
+        <v>6924711</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2549,7 +2559,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2559,7 +2569,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,10 +2596,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125120869</v>
+        <v>125121813</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2598,33 +2608,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
@@ -2634,7 +2639,7 @@
         <v>596348</v>
       </c>
       <c r="R18" t="n">
-        <v>6924552</v>
+        <v>6924619</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2666,7 +2671,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2676,12 +2681,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125121984</v>
+        <v>125121336</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,27 +1286,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596332</v>
+        <v>596327</v>
       </c>
       <c r="R7" t="n">
-        <v>6924612</v>
+        <v>6924526</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1504,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125121336</v>
+        <v>125121984</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,27 +1520,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596327</v>
+        <v>596332</v>
       </c>
       <c r="R9" t="n">
-        <v>6924526</v>
+        <v>6924612</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125126464</v>
+        <v>125123246</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596305</v>
+        <v>596268</v>
       </c>
       <c r="R2" t="n">
-        <v>6924608</v>
+        <v>6924738</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123531</v>
+        <v>125123659</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596208</v>
+        <v>596186</v>
       </c>
       <c r="R3" t="n">
-        <v>6924703</v>
+        <v>6924711</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125122129</v>
+        <v>125126330</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596387</v>
+        <v>596310</v>
       </c>
       <c r="R4" t="n">
-        <v>6924499</v>
+        <v>6924614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två talltitor I gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,19 +1014,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125121863</v>
+        <v>125126858</v>
       </c>
       <c r="B5" t="n">
         <v>57666</v>
@@ -1064,22 +1059,36 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596311</v>
+        <v>596293</v>
       </c>
       <c r="R5" t="n">
-        <v>6924570</v>
+        <v>6924558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,22 +1145,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125125242</v>
+        <v>125122129</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,39 +1173,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596305</v>
+        <v>596387</v>
       </c>
       <c r="R6" t="n">
-        <v>6924653</v>
+        <v>6924499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,12 +1247,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Två talltitor I gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,22 +1267,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125121336</v>
+        <v>125121984</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>57883</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,27 +1295,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596327</v>
+        <v>596332</v>
       </c>
       <c r="R7" t="n">
-        <v>6924526</v>
+        <v>6924612</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125123246</v>
+        <v>125121863</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,38 +1408,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596268</v>
+        <v>596311</v>
       </c>
       <c r="R8" t="n">
-        <v>6924738</v>
+        <v>6924570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,12 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125121984</v>
+        <v>125121813</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,39 +1529,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596332</v>
+        <v>596348</v>
       </c>
       <c r="R9" t="n">
-        <v>6924612</v>
+        <v>6924619</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,7 +1625,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123156</v>
+        <v>125122523</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1657,7 +1661,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1666,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596286</v>
+        <v>596319</v>
       </c>
       <c r="R10" t="n">
-        <v>6924710</v>
+        <v>6924626</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1720,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
+          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125126858</v>
+        <v>125120869</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,53 +1763,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596293</v>
+        <v>596348</v>
       </c>
       <c r="R11" t="n">
-        <v>6924558</v>
+        <v>6924552</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,7 +1827,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1847,7 +1837,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,19 +1857,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125122523</v>
+        <v>125126936</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1919,10 +1914,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596319</v>
+        <v>596309</v>
       </c>
       <c r="R12" t="n">
-        <v>6924626</v>
+        <v>6924544</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1949,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,12 +1959,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,19 +1979,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125126976</v>
+        <v>125125242</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -2041,10 +2036,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596409</v>
+        <v>596305</v>
       </c>
       <c r="R13" t="n">
-        <v>6924486</v>
+        <v>6924653</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,7 +2071,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2086,7 +2081,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2118,7 +2113,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125126936</v>
+        <v>125123156</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2154,7 +2149,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596309</v>
+        <v>596286</v>
       </c>
       <c r="R14" t="n">
-        <v>6924544</v>
+        <v>6924710</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2198,7 +2193,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2208,12 +2203,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,22 +2223,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125126271</v>
+        <v>125123531</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2256,16 +2251,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2285,10 +2280,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596310</v>
+        <v>596208</v>
       </c>
       <c r="R15" t="n">
-        <v>6924614</v>
+        <v>6924703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2320,7 +2315,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2330,12 +2325,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2362,10 +2352,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125120869</v>
+        <v>125121336</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2374,31 +2364,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2407,10 +2397,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596348</v>
+        <v>596327</v>
       </c>
       <c r="R16" t="n">
-        <v>6924552</v>
+        <v>6924526</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2442,7 +2432,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2452,12 +2442,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>07:13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2484,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125123659</v>
+        <v>125126976</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2500,34 +2485,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596186</v>
+        <v>596409</v>
       </c>
       <c r="R17" t="n">
-        <v>6924711</v>
+        <v>6924486</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2559,7 +2549,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2569,7 +2559,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2596,10 +2591,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125121813</v>
+        <v>125126464</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2608,38 +2603,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596348</v>
+        <v>596305</v>
       </c>
       <c r="R18" t="n">
-        <v>6924619</v>
+        <v>6924608</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,12 +2696,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123659</v>
+        <v>125126858</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +808,53 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596186</v>
+        <v>596293</v>
       </c>
       <c r="R3" t="n">
-        <v>6924711</v>
+        <v>6924558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +911,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125126330</v>
+        <v>125123659</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +939,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596310</v>
+        <v>596186</v>
       </c>
       <c r="R4" t="n">
-        <v>6924614</v>
+        <v>6924711</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125126858</v>
+        <v>125126330</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,53 +1051,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596293</v>
+        <v>596310</v>
       </c>
       <c r="R5" t="n">
-        <v>6924558</v>
+        <v>6924614</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,12 +1145,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125126976</v>
+        <v>125126464</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2485,16 +2485,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596409</v>
+        <v>596305</v>
       </c>
       <c r="R17" t="n">
-        <v>6924486</v>
+        <v>6924608</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2559,12 +2559,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2579,22 +2574,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125126464</v>
+        <v>125126976</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,16 +2602,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2636,10 +2631,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596305</v>
+        <v>596409</v>
       </c>
       <c r="R18" t="n">
-        <v>6924608</v>
+        <v>6924486</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2671,7 +2666,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2681,7 +2676,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,12 +2696,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123246</v>
+        <v>125121984</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>57883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596268</v>
+        <v>596332</v>
       </c>
       <c r="R2" t="n">
-        <v>6924738</v>
+        <v>6924612</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125126858</v>
+        <v>125125242</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,53 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596293</v>
+        <v>596305</v>
       </c>
       <c r="R3" t="n">
-        <v>6924558</v>
+        <v>6924653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +902,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123659</v>
+        <v>125121863</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,34 +930,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596186</v>
+        <v>596311</v>
       </c>
       <c r="R4" t="n">
-        <v>6924711</v>
+        <v>6924570</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1157,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125122129</v>
+        <v>125123659</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,39 +1169,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596387</v>
+        <v>596186</v>
       </c>
       <c r="R6" t="n">
-        <v>6924499</v>
+        <v>6924711</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,12 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Två talltitor I gran</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,22 +1253,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125121984</v>
+        <v>125122523</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,20 +1277,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1315,7 +1301,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1324,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596332</v>
+        <v>596319</v>
       </c>
       <c r="R7" t="n">
-        <v>6924612</v>
+        <v>6924626</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1355,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125121863</v>
+        <v>125126976</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,27 +1403,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1441,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596311</v>
+        <v>596409</v>
       </c>
       <c r="R8" t="n">
-        <v>6924570</v>
+        <v>6924486</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1477,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125121813</v>
+        <v>125122129</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,38 +1521,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596348</v>
+        <v>596387</v>
       </c>
       <c r="R9" t="n">
-        <v>6924619</v>
+        <v>6924499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1598,7 +1599,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Två talltitor I gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,22 +1619,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125122523</v>
+        <v>125123531</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,16 +1647,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1661,7 +1667,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1670,10 +1676,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596319</v>
+        <v>596208</v>
       </c>
       <c r="R10" t="n">
-        <v>6924626</v>
+        <v>6924703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1711,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,12 +1721,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1869,10 +1870,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125126936</v>
+        <v>125126858</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,39 +1886,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596309</v>
+        <v>596293</v>
       </c>
       <c r="R12" t="n">
-        <v>6924544</v>
+        <v>6924558</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1949,7 +1964,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1959,12 +1974,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125125242</v>
+        <v>125121813</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2003,43 +2013,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596305</v>
+        <v>596348</v>
       </c>
       <c r="R13" t="n">
-        <v>6924653</v>
+        <v>6924619</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2071,7 +2076,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2081,12 +2086,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2235,7 +2235,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125123531</v>
+        <v>125126464</v>
       </c>
       <c r="B15" t="n">
         <v>57529</v>
@@ -2271,7 +2271,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596208</v>
+        <v>596305</v>
       </c>
       <c r="R15" t="n">
-        <v>6924703</v>
+        <v>6924608</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2340,22 +2340,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125121336</v>
+        <v>125123246</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2368,39 +2368,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596327</v>
+        <v>596268</v>
       </c>
       <c r="R16" t="n">
-        <v>6924526</v>
+        <v>6924738</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2432,7 +2427,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2442,7 +2437,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,10 +2469,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125126464</v>
+        <v>125121336</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,31 +2481,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596305</v>
+        <v>596327</v>
       </c>
       <c r="R17" t="n">
-        <v>6924608</v>
+        <v>6924526</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,19 +2574,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125126976</v>
+        <v>125126936</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596409</v>
+        <v>596309</v>
       </c>
       <c r="R18" t="n">
-        <v>6924486</v>
+        <v>6924544</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,12 +2696,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125121984</v>
+        <v>125126858</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,57 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596332</v>
+        <v>596293</v>
       </c>
       <c r="R2" t="n">
-        <v>6924612</v>
+        <v>6924558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +794,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125125242</v>
+        <v>125120869</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,7 +842,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596305</v>
+        <v>596348</v>
       </c>
       <c r="R3" t="n">
-        <v>6924653</v>
+        <v>6924552</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -914,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125121863</v>
+        <v>125122129</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,14 +969,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596311</v>
+        <v>596387</v>
       </c>
       <c r="R4" t="n">
-        <v>6924570</v>
+        <v>6924499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1018,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Två talltitor I gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1038,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125126330</v>
+        <v>125121984</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>58001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,20 +1062,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1067,7 +1086,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596310</v>
+        <v>596332</v>
       </c>
       <c r="R5" t="n">
-        <v>6924614</v>
+        <v>6924612</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123659</v>
+        <v>125121813</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>97147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,25 +1179,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596186</v>
+        <v>596348</v>
       </c>
       <c r="R6" t="n">
-        <v>6924711</v>
+        <v>6924619</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125122523</v>
+        <v>125126271</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,7 +1315,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1310,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596319</v>
+        <v>596310</v>
       </c>
       <c r="R7" t="n">
-        <v>6924626</v>
+        <v>6924614</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1369,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125126976</v>
+        <v>125125242</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,10 +1446,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596409</v>
+        <v>596305</v>
       </c>
       <c r="R8" t="n">
-        <v>6924486</v>
+        <v>6924653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1509,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125122129</v>
+        <v>125122523</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,39 +1539,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596387</v>
+        <v>596319</v>
       </c>
       <c r="R9" t="n">
-        <v>6924499</v>
+        <v>6924626</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,7 +1603,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1599,12 +1613,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Två talltitor I gran</t>
+          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,22 +1633,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123531</v>
+        <v>125121336</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>56836</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1643,31 +1657,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1676,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596208</v>
+        <v>596327</v>
       </c>
       <c r="R10" t="n">
-        <v>6924703</v>
+        <v>6924526</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,7 +1725,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1721,7 +1735,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,10 +1762,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125120869</v>
+        <v>125123156</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1793,10 +1807,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596348</v>
+        <v>596286</v>
       </c>
       <c r="R11" t="n">
-        <v>6924552</v>
+        <v>6924710</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,7 +1842,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,12 +1852,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1870,10 +1884,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125126858</v>
+        <v>125123531</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1886,53 +1900,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596293</v>
+        <v>596208</v>
       </c>
       <c r="R12" t="n">
-        <v>6924558</v>
+        <v>6924703</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1989,22 +1989,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125121813</v>
+        <v>125126936</v>
       </c>
       <c r="B13" t="n">
-        <v>96979</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,38 +2013,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596348</v>
+        <v>596309</v>
       </c>
       <c r="R13" t="n">
-        <v>6924619</v>
+        <v>6924544</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,7 +2081,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2086,7 +2091,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2101,22 +2111,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125123156</v>
+        <v>125126976</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2149,7 +2159,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2158,10 +2168,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596286</v>
+        <v>596409</v>
       </c>
       <c r="R14" t="n">
-        <v>6924710</v>
+        <v>6924486</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2193,7 +2203,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2203,12 +2213,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2235,10 +2245,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125126464</v>
+        <v>125121863</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>57793</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,27 +2261,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2280,10 +2290,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596305</v>
+        <v>596311</v>
       </c>
       <c r="R15" t="n">
-        <v>6924608</v>
+        <v>6924570</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2315,7 +2325,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2325,7 +2335,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2340,12 +2350,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2355,7 +2365,7 @@
         <v>125123246</v>
       </c>
       <c r="B16" t="n">
-        <v>96979</v>
+        <v>97147</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2469,10 +2479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125121336</v>
+        <v>125126464</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>57632</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,31 +2491,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2514,10 +2524,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596327</v>
+        <v>596305</v>
       </c>
       <c r="R17" t="n">
-        <v>6924526</v>
+        <v>6924608</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2549,7 +2559,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2559,7 +2569,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,22 +2584,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125126936</v>
+        <v>125123659</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2602,39 +2612,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596309</v>
+        <v>596186</v>
       </c>
       <c r="R18" t="n">
-        <v>6924544</v>
+        <v>6924711</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2666,7 +2671,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2676,12 +2681,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,12 +2696,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -1645,10 +1645,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125121336</v>
+        <v>125123156</v>
       </c>
       <c r="B10" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1657,31 +1657,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596327</v>
+        <v>596286</v>
       </c>
       <c r="R10" t="n">
-        <v>6924526</v>
+        <v>6924710</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,7 +1735,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,10 +1767,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125123156</v>
+        <v>125121336</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1774,31 +1779,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1807,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596286</v>
+        <v>596327</v>
       </c>
       <c r="R11" t="n">
-        <v>6924710</v>
+        <v>6924526</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,7 +1847,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1852,12 +1857,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2479,10 +2479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125126464</v>
+        <v>125123659</v>
       </c>
       <c r="B17" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,39 +2495,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596305</v>
+        <v>596186</v>
       </c>
       <c r="R17" t="n">
-        <v>6924608</v>
+        <v>6924711</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2559,7 +2554,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2569,7 +2564,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2584,22 +2579,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125123659</v>
+        <v>125126464</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2612,34 +2607,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596186</v>
+        <v>596305</v>
       </c>
       <c r="R18" t="n">
-        <v>6924711</v>
+        <v>6924608</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,12 +2696,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125126858</v>
+        <v>125121984</v>
       </c>
       <c r="B2" t="n">
-        <v>57793</v>
+        <v>58001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,57 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596293</v>
+        <v>596332</v>
       </c>
       <c r="R2" t="n">
-        <v>6924558</v>
+        <v>6924612</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +780,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -928,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125122129</v>
+        <v>125126976</v>
       </c>
       <c r="B4" t="n">
-        <v>57793</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,39 +930,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596387</v>
+        <v>596409</v>
       </c>
       <c r="R4" t="n">
-        <v>6924499</v>
+        <v>6924486</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,12 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två talltitor I gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,22 +1024,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125121984</v>
+        <v>125121336</v>
       </c>
       <c r="B5" t="n">
-        <v>58001</v>
+        <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,27 +1052,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1095,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596332</v>
+        <v>596327</v>
       </c>
       <c r="R5" t="n">
-        <v>6924612</v>
+        <v>6924526</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125121813</v>
+        <v>125123659</v>
       </c>
       <c r="B6" t="n">
-        <v>97147</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,25 +1165,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1207,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596348</v>
+        <v>596186</v>
       </c>
       <c r="R6" t="n">
-        <v>6924619</v>
+        <v>6924711</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125126271</v>
+        <v>125122523</v>
       </c>
       <c r="B7" t="n">
         <v>57635</v>
@@ -1315,7 +1301,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1324,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596310</v>
+        <v>596319</v>
       </c>
       <c r="R7" t="n">
-        <v>6924614</v>
+        <v>6924626</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,12 +1355,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,7 +1387,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125125242</v>
+        <v>125126936</v>
       </c>
       <c r="B8" t="n">
         <v>57635</v>
@@ -1446,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596305</v>
+        <v>596309</v>
       </c>
       <c r="R8" t="n">
-        <v>6924653</v>
+        <v>6924544</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,12 +1477,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,22 +1497,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125122523</v>
+        <v>125126858</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>57793</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,39 +1525,53 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596319</v>
+        <v>596293</v>
       </c>
       <c r="R9" t="n">
-        <v>6924626</v>
+        <v>6924558</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1613,12 +1613,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ett ringhack på tall. Pga lite dålig sikt är jag inte helt säker, men jag tror det är ett ringhack.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,22 +1628,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125123156</v>
+        <v>125126464</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1661,16 +1656,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1681,7 +1676,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1690,10 +1685,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596286</v>
+        <v>596305</v>
       </c>
       <c r="R10" t="n">
-        <v>6924710</v>
+        <v>6924608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1725,7 +1720,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,12 +1730,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,22 +1745,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125121336</v>
+        <v>125123531</v>
       </c>
       <c r="B11" t="n">
-        <v>56836</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1779,31 +1769,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1812,10 +1802,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596327</v>
+        <v>596208</v>
       </c>
       <c r="R11" t="n">
-        <v>6924526</v>
+        <v>6924703</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1847,7 +1837,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1857,7 +1847,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1884,10 +1874,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125123531</v>
+        <v>125121863</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
+        <v>57793</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1900,27 +1890,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1929,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596208</v>
+        <v>596311</v>
       </c>
       <c r="R12" t="n">
-        <v>6924703</v>
+        <v>6924570</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1964,7 +1954,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1964,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2001,10 +1991,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125126936</v>
+        <v>125123246</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
+        <v>97147</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,43 +2003,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596309</v>
+        <v>596268</v>
       </c>
       <c r="R13" t="n">
-        <v>6924544</v>
+        <v>6924738</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2081,7 +2066,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2091,12 +2076,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Rikligt med revlummer</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2111,19 +2096,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125126976</v>
+        <v>125125242</v>
       </c>
       <c r="B14" t="n">
         <v>57635</v>
@@ -2168,10 +2153,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596409</v>
+        <v>596305</v>
       </c>
       <c r="R14" t="n">
-        <v>6924486</v>
+        <v>6924653</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2203,7 +2188,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2213,7 +2198,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2245,10 +2230,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125121863</v>
+        <v>125123156</v>
       </c>
       <c r="B15" t="n">
-        <v>57793</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2261,27 +2246,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2290,10 +2275,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596311</v>
+        <v>596286</v>
       </c>
       <c r="R15" t="n">
-        <v>6924570</v>
+        <v>6924710</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2325,7 +2310,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2335,7 +2320,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2362,7 +2352,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125123246</v>
+        <v>125121813</v>
       </c>
       <c r="B16" t="n">
         <v>97147</v>
@@ -2402,10 +2392,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596268</v>
+        <v>596348</v>
       </c>
       <c r="R16" t="n">
-        <v>6924738</v>
+        <v>6924619</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2437,7 +2427,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2447,12 +2437,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2479,10 +2464,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125123659</v>
+        <v>125126330</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,34 +2480,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596186</v>
+        <v>596310</v>
       </c>
       <c r="R17" t="n">
-        <v>6924711</v>
+        <v>6924614</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2554,7 +2544,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2564,7 +2554,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2591,10 +2586,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125126464</v>
+        <v>125122129</v>
       </c>
       <c r="B18" t="n">
-        <v>57632</v>
+        <v>57793</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,39 +2602,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596305</v>
+        <v>596387</v>
       </c>
       <c r="R18" t="n">
-        <v>6924608</v>
+        <v>6924499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2671,7 +2666,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2681,7 +2676,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två talltitor I gran</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -1874,10 +1874,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125121863</v>
+        <v>125125242</v>
       </c>
       <c r="B12" t="n">
-        <v>57793</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1890,27 +1890,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596311</v>
+        <v>596305</v>
       </c>
       <c r="R12" t="n">
-        <v>6924570</v>
+        <v>6924653</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,7 +1964,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,10 +1996,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125123246</v>
+        <v>125123156</v>
       </c>
       <c r="B13" t="n">
-        <v>97147</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2003,38 +2008,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596268</v>
+        <v>596286</v>
       </c>
       <c r="R13" t="n">
-        <v>6924738</v>
+        <v>6924710</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2066,7 +2076,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2076,12 +2086,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med revlummer</t>
+          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,10 +2118,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125125242</v>
+        <v>125121863</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
+        <v>57793</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2124,27 +2134,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2153,10 +2163,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596305</v>
+        <v>596311</v>
       </c>
       <c r="R14" t="n">
-        <v>6924653</v>
+        <v>6924570</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,7 +2198,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2198,12 +2208,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2230,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125123156</v>
+        <v>125123246</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
+        <v>97147</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2242,43 +2247,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596286</v>
+        <v>596268</v>
       </c>
       <c r="R15" t="n">
-        <v>6924710</v>
+        <v>6924738</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
+          <t>Rikligt med revlummer</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125121984</v>
+        <v>125123246</v>
       </c>
       <c r="B2" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596332</v>
+        <v>596268</v>
       </c>
       <c r="R2" t="n">
-        <v>6924612</v>
+        <v>6924738</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125120869</v>
+        <v>125125242</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,7 +818,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596348</v>
+        <v>596305</v>
       </c>
       <c r="R3" t="n">
-        <v>6924552</v>
+        <v>6924653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -914,15 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125126976</v>
+        <v>125123531</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -950,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596409</v>
+        <v>596208</v>
       </c>
       <c r="R4" t="n">
-        <v>6924486</v>
+        <v>6924703</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,55 +1016,64 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125121336</v>
+        <v>125126858</v>
       </c>
       <c r="B5" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran , Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596327</v>
+        <v>596293</v>
       </c>
       <c r="R5" t="n">
-        <v>6924526</v>
+        <v>6924558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,12 +1130,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1156,12 +1145,7 @@
         <v>125123659</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,12 +1252,7 @@
         <v>125122523</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,55 +1366,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125126936</v>
+        <v>125121813</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596309</v>
+        <v>596348</v>
       </c>
       <c r="R8" t="n">
-        <v>6924544</v>
+        <v>6924619</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,12 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,27 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125126858</v>
+        <v>125126936</v>
       </c>
       <c r="B9" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,53 +1484,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596293</v>
+        <v>596309</v>
       </c>
       <c r="R9" t="n">
-        <v>6924558</v>
+        <v>6924544</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1613,7 +1558,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1640,15 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125126464</v>
+        <v>125122129</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,39 +1601,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596305</v>
+        <v>596387</v>
       </c>
       <c r="R10" t="n">
-        <v>6924608</v>
+        <v>6924499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1730,7 +1675,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Två talltitor I gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,15 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125123531</v>
+        <v>125126271</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,16 +1718,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1802,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596208</v>
+        <v>596310</v>
       </c>
       <c r="R11" t="n">
-        <v>6924703</v>
+        <v>6924614</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1847,7 +1792,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,43 +1824,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125125242</v>
+        <v>125121336</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1919,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596305</v>
+        <v>596327</v>
       </c>
       <c r="R12" t="n">
-        <v>6924653</v>
+        <v>6924526</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,12 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1999,12 +1939,7 @@
         <v>125123156</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2118,43 +2053,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125121863</v>
+        <v>125121984</v>
       </c>
       <c r="B14" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2163,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596311</v>
+        <v>596332</v>
       </c>
       <c r="R14" t="n">
-        <v>6924570</v>
+        <v>6924612</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2198,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2208,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2235,50 +2165,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125123246</v>
+        <v>125126976</v>
       </c>
       <c r="B15" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596268</v>
+        <v>596409</v>
       </c>
       <c r="R15" t="n">
-        <v>6924738</v>
+        <v>6924486</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2310,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2320,12 +2250,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt med revlummer</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2352,50 +2282,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125121813</v>
+        <v>125126464</v>
       </c>
       <c r="B16" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596348</v>
+        <v>596305</v>
       </c>
       <c r="R16" t="n">
-        <v>6924619</v>
+        <v>6924608</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2427,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2437,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,27 +2382,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125126330</v>
+        <v>125120869</v>
       </c>
       <c r="B17" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2509,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596310</v>
+        <v>596348</v>
       </c>
       <c r="R17" t="n">
-        <v>6924614</v>
+        <v>6924552</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2544,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2554,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2586,15 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125122129</v>
+        <v>125121863</v>
       </c>
       <c r="B18" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,14 +2547,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596387</v>
+        <v>596311</v>
       </c>
       <c r="R18" t="n">
-        <v>6924499</v>
+        <v>6924570</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2666,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2676,12 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två talltitor I gran</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,12 +2611,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125125242</v>
+        <v>125123531</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -818,7 +818,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596305</v>
+        <v>596208</v>
       </c>
       <c r="R3" t="n">
-        <v>6924653</v>
+        <v>6924703</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125123531</v>
+        <v>125125242</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,16 +910,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,7 +930,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596208</v>
+        <v>596305</v>
       </c>
       <c r="R4" t="n">
-        <v>6924703</v>
+        <v>6924653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125123531</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>125126464</v>
       </c>
       <c r="B16" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125123531</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>125126464</v>
       </c>
       <c r="B16" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125123531</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>125126464</v>
       </c>
       <c r="B16" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125123531</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>125126464</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125123531</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>125126464</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125123531</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>125126464</v>
       </c>
       <c r="B16" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>125125242</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>125122523</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>125126936</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>125126271</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>125123156</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>125126976</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>125120869</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>125125242</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>125122523</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>125126936</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>125126271</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>125123156</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>125126976</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>125120869</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123246</v>
+        <v>125127163</v>
       </c>
       <c r="B2" t="n">
-        <v>97202</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596268</v>
+        <v>596407</v>
       </c>
       <c r="R2" t="n">
-        <v>6924738</v>
+        <v>6924497</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125123531</v>
+        <v>125123659</v>
       </c>
       <c r="B3" t="n">
-        <v>57681</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596208</v>
+        <v>596186</v>
       </c>
       <c r="R3" t="n">
-        <v>6924703</v>
+        <v>6924711</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125125242</v>
+        <v>125123531</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,7 +920,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596305</v>
+        <v>596208</v>
       </c>
       <c r="R4" t="n">
-        <v>6924653</v>
+        <v>6924703</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,64 +1001,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125126858</v>
+        <v>125126464</v>
       </c>
       <c r="B5" t="n">
-        <v>57811</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ladmyran , Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596293</v>
+        <v>596305</v>
       </c>
       <c r="R5" t="n">
-        <v>6924558</v>
+        <v>6924608</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125123659</v>
+        <v>125120869</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,34 +1124,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596186</v>
+        <v>596348</v>
       </c>
       <c r="R6" t="n">
-        <v>6924711</v>
+        <v>6924552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1198,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,7 +1233,7 @@
         <v>125122523</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,45 +1347,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125121813</v>
+        <v>125123156</v>
       </c>
       <c r="B8" t="n">
-        <v>97202</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596348</v>
+        <v>596286</v>
       </c>
       <c r="R8" t="n">
-        <v>6924619</v>
+        <v>6924710</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1432,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125126936</v>
+        <v>125125242</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596309</v>
+        <v>596305</v>
       </c>
       <c r="R9" t="n">
-        <v>6924544</v>
+        <v>6924653</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,12 +1549,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,22 +1569,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125122129</v>
+        <v>125126271</v>
       </c>
       <c r="B10" t="n">
-        <v>57811</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,39 +1592,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
+          <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596387</v>
+        <v>596310</v>
       </c>
       <c r="R10" t="n">
-        <v>6924499</v>
+        <v>6924614</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,12 +1666,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Två talltitor I gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,22 +1686,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125126271</v>
+        <v>125126936</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1729,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1747,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596310</v>
+        <v>596309</v>
       </c>
       <c r="R11" t="n">
-        <v>6924614</v>
+        <v>6924544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,12 +1783,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,50 +1803,50 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125121336</v>
+        <v>125126976</v>
       </c>
       <c r="B12" t="n">
-        <v>56843</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1864,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596327</v>
+        <v>596409</v>
       </c>
       <c r="R12" t="n">
-        <v>6924526</v>
+        <v>6924486</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1900,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,38 +1932,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125123156</v>
+        <v>124923951</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596286</v>
+        <v>596267</v>
       </c>
       <c r="R13" t="n">
-        <v>6924710</v>
+        <v>6924542</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,27 +2006,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fler hack även längre upp på trädet. Färsk kåda som runnit ner.</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125121984</v>
+        <v>125121336</v>
       </c>
       <c r="B14" t="n">
-        <v>58019</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,27 +2059,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2093,10 +2088,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596332</v>
+        <v>596327</v>
       </c>
       <c r="R14" t="n">
-        <v>6924612</v>
+        <v>6924526</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2123,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2133,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,50 +2160,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125126976</v>
+        <v>125121538</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ladmyran, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596409</v>
+        <v>596405</v>
       </c>
       <c r="R15" t="n">
-        <v>6924486</v>
+        <v>6924495</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,7 +2238,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,12 +2248,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Färska spår tjäder</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,39 +2268,39 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125126464</v>
+        <v>125121984</v>
       </c>
       <c r="B16" t="n">
-        <v>57681</v>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2313,7 +2311,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2322,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596305</v>
+        <v>596332</v>
       </c>
       <c r="R16" t="n">
-        <v>6924608</v>
+        <v>6924612</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,22 +2380,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125120869</v>
+        <v>125121863</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,27 +2403,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2434,10 +2432,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596348</v>
+        <v>596311</v>
       </c>
       <c r="R17" t="n">
-        <v>6924552</v>
+        <v>6924570</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,12 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125121863</v>
+        <v>125122129</v>
       </c>
       <c r="B18" t="n">
-        <v>57811</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,14 +2540,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Ladmyran, Svarttjärnåsen, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596311</v>
+        <v>596387</v>
       </c>
       <c r="R18" t="n">
-        <v>6924570</v>
+        <v>6924499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,7 +2579,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2589,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två talltitor I gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,15 +2609,461 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125126858</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ladmyran , Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>596293</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6924558</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130155316</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tjärdalsberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>596229</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6924771</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125121813</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>596348</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6924619</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125123246</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>596268</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6924738</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125127163</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125123659</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125123531</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125126464</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125120869</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125122523</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125123156</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1578,6 +1618,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125125242</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1695,6 +1740,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125126271</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125126936</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1929,6 +1984,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125126976</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2045,6 +2105,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124923951</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2157,6 +2222,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125121336</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2277,6 +2347,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125121538</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2389,6 +2464,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125121984</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2501,6 +2581,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125121863</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2618,6 +2703,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125122129</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2744,6 +2834,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125126858</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2845,6 +2940,11 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155316</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2952,6 +3052,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125121813</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3064,8 +3169,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125123246</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2842,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130155316</v>
+        <v>136444071</v>
       </c>
       <c r="B20" t="n">
-        <v>99035</v>
+        <v>56860</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,34 +2853,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>205992</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tjärdalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596229</v>
+        <v>596327</v>
       </c>
       <c r="R20" t="n">
-        <v>6924771</v>
+        <v>6924562</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2907,12 +2916,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2927,12 +2946,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johanna Kühne</t>
+          <t>Magnus Lundquist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johanna Kühne</t>
+          <t>Magnus Lundquist, Paulina Wietrzyk-Pelka</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2942,51 +2961,56 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130155316</t>
+          <t>https://artportalen.se/Sighting/136444071</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125121813</v>
+        <v>136444067</v>
       </c>
       <c r="B21" t="n">
-        <v>97983</v>
+        <v>56851</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>205998</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Tjärdalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596348</v>
+        <v>596327</v>
       </c>
       <c r="R21" t="n">
-        <v>6924619</v>
+        <v>6924562</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3013,22 +3037,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3043,27 +3067,31 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Magnus Lundquist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Magnus Lundquist, Paulina Wietrzyk-Pelka</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125121813</t>
+          <t>https://artportalen.se/Sighting/136444067</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125123246</v>
+        <v>130155316</v>
       </c>
       <c r="B22" t="n">
-        <v>97983</v>
+        <v>99035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,34 +3099,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ladmyran, Mpd</t>
+          <t>Tjärdalsberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596268</v>
+        <v>596229</v>
       </c>
       <c r="R22" t="n">
-        <v>6924738</v>
+        <v>6924771</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3125,27 +3153,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:12</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt med revlummer</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3160,16 +3173,249 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130155316</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125121813</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>596348</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6924619</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125121813</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125123246</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ladmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>596268</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6924738</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt med revlummer</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125123246</t>
         </is>
@@ -3198,6 +3444,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37814-2023 artfynd.xlsx
+++ b/artfynd/A 37814-2023 artfynd.xlsx
@@ -2845,7 +2845,7 @@
         <v>136444071</v>
       </c>
       <c r="B20" t="n">
-        <v>56860</v>
+        <v>56873</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>136444067</v>
       </c>
       <c r="B21" t="n">
-        <v>56851</v>
+        <v>56864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
